--- a/PROYECTO_CIGARS_CUBA_2027/07_OPERATIONS/Risk Register.xlsx
+++ b/PROYECTO_CIGARS_CUBA_2027/07_OPERATIONS/Risk Register.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="284">
   <si>
     <t xml:space="preserve">Registro de riesgos — Proyectos A, B y C</t>
   </si>
@@ -443,13 +443,58 @@
     <t xml:space="preserve">Sólo importaciones declaradas y habilitadas</t>
   </si>
   <si>
+    <t xml:space="preserve">R29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marca / persona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arnaldo retira su colaboración, fallece o entra en conflicto: la marca lleva su nombre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marca de nombre propio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licencia de nombre/firma irrevocable y transferible; cláusulas leaver y fallecimiento; derecho de recompra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cambio de actitud / situación laboral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El empleador de Arnaldo o una entidad cubana reclama la marca o su nombre (precedentes Davidoff y Vegas Robaina)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación dentro del sistema estatal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registro previo UE y Cuba a nombre de la SL; autorización escrita del empleador; cláusula de titularidad en contrato de fabricación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asociación con Arnaldo Vichot (ex maestro ligador de Partagás) o confusión con ARLONDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de pila común</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registrar con apellido y firma; no sugerir vínculo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Informe de registrabilidad</t>
+  </si>
+  <si>
     <t xml:space="preserve">R22</t>
   </si>
   <si>
-    <t xml:space="preserve">Marca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oposición o colisión de la marca FOLIO en clase 34</t>
+    <t xml:space="preserve">Oposición o colisión de la marca ARNALDO en clase 34</t>
   </si>
   <si>
     <t xml:space="preserve">Búsqueda preliminar no oficial</t>
@@ -638,7 +683,7 @@
     <t xml:space="preserve">DL 203/1999 de marcas; registro OCPI vía agente oficial</t>
   </si>
   <si>
-    <t xml:space="preserve">Necesario registrar FOLIO en Cuba</t>
+    <t xml:space="preserve">Necesario registrar ARNALDO (a nombre de la SL) en Cuba</t>
   </si>
   <si>
     <t xml:space="preserve">PROBABLE (S42)</t>
@@ -1285,7 +1330,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -2189,7 +2234,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
         <v>140</v>
       </c>
@@ -2209,18 +2254,18 @@
         <v>2</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H26" s="6" t="n">
         <f aca="false">F26*G26</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I26" s="7" t="str">
         <f aca="false">IF(H26&gt;=15,"Crítico",IF(H26&gt;=8,"Alto","Medio/bajo"))</f>
         <v>Alto</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="K26" s="4" t="s">
         <v>144</v>
@@ -2229,221 +2274,221 @@
         <v>145</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
         <v>146</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="E27" s="4" t="s">
         <v>148</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>150</v>
       </c>
       <c r="F27" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H27" s="6" t="n">
         <f aca="false">F27*G27</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I27" s="7" t="str">
         <f aca="false">IF(H27&gt;=15,"Crítico",IF(H27&gt;=8,"Alto","Medio/bajo"))</f>
-        <v>Alto</v>
+        <v>Crítico</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>151</v>
+        <v>31</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>155</v>
-      </c>
       <c r="F28" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="5" t="n">
         <v>3</v>
       </c>
       <c r="H28" s="6" t="n">
         <f aca="false">F28*G28</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I28" s="7" t="str">
         <f aca="false">IF(H28&gt;=15,"Crítico",IF(H28&gt;=8,"Alto","Medio/bajo"))</f>
-        <v>Alto</v>
+        <v>Medio/bajo</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>151</v>
+        <v>43</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H29" s="6" t="n">
         <f aca="false">F29*G29</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I29" s="7" t="str">
         <f aca="false">IF(H29&gt;=15,"Crítico",IF(H29&gt;=8,"Alto","Medio/bajo"))</f>
         <v>Alto</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="D30" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" s="4" t="s">
+      <c r="E30" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>166</v>
-      </c>
       <c r="F30" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" s="5" t="n">
         <v>4</v>
       </c>
       <c r="H30" s="6" t="n">
         <f aca="false">F30*G30</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I30" s="7" t="str">
         <f aca="false">IF(H30&gt;=15,"Crítico",IF(H30&gt;=8,"Alto","Medio/bajo"))</f>
         <v>Alto</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>50</v>
+        <v>166</v>
       </c>
       <c r="K30" s="4" t="s">
         <v>167</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>168</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="E31" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>172</v>
-      </c>
       <c r="F31" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H31" s="6" t="n">
         <f aca="false">F31*G31</f>
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I31" s="7" t="str">
         <f aca="false">IF(H31&gt;=15,"Crítico",IF(H31&gt;=8,"Alto","Medio/bajo"))</f>
-        <v>Crítico</v>
+        <v>Alto</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>50</v>
+        <v>166</v>
       </c>
       <c r="K31" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="L31" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="L31" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="s">
+      <c r="B32" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="C32" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="C32" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="D32" s="4" t="s">
+      <c r="E32" s="4" t="s">
         <v>176</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>177</v>
       </c>
       <c r="F32" s="5" t="n">
         <v>3</v>
@@ -2463,28 +2508,148 @@
         <v>50</v>
       </c>
       <c r="K32" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="L32" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="L32" s="4" t="s">
+      <c r="B33" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <f aca="false">F33*G33</f>
+        <v>8</v>
+      </c>
+      <c r="I33" s="7" t="str">
+        <f aca="false">IF(H33&gt;=15,"Crítico",IF(H33&gt;=8,"Alto","Medio/bajo"))</f>
+        <v>Alto</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="L33" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <f aca="false">F34*G34</f>
+        <v>16</v>
+      </c>
+      <c r="I34" s="7" t="str">
+        <f aca="false">IF(H34&gt;=15,"Crítico",IF(H34&gt;=8,"Alto","Medio/bajo"))</f>
+        <v>Crítico</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="L34" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <f aca="false">F35*G35</f>
+        <v>9</v>
+      </c>
+      <c r="I35" s="7" t="str">
+        <f aca="false">IF(H35&gt;=15,"Crítico",IF(H35&gt;=8,"Alto","Medio/bajo"))</f>
+        <v>Alto</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="L35" s="4" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D34" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="H34" s="9" t="n">
-        <f aca="false">COUNTIF(I5:I32,"Crítico")</f>
-        <v>9</v>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D37" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="H37" s="9" t="n">
+        <f aca="false">COUNTIF(I5:I35,"Crítico")</f>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="I5:I32">
+  <conditionalFormatting sqref="I5:I35">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"Crítico"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H32">
+  <conditionalFormatting sqref="H5:H35">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="1"/>
@@ -2522,128 +2687,128 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>134</v>
@@ -2651,16 +2816,16 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>81</v>
@@ -2668,50 +2833,50 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>134</v>
@@ -2719,33 +2884,33 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>128</v>
@@ -2753,33 +2918,33 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>134</v>
@@ -2787,84 +2952,84 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>134</v>
@@ -2872,16 +3037,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>70</v>
@@ -2889,19 +3054,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>

--- a/PROYECTO_CIGARS_CUBA_2027/07_OPERATIONS/Risk Register.xlsx
+++ b/PROYECTO_CIGARS_CUBA_2027/07_OPERATIONS/Risk Register.xlsx
@@ -479,13 +479,13 @@
     <t xml:space="preserve">Marca</t>
   </si>
   <si>
-    <t xml:space="preserve">Asociación con Arnaldo Vichot (ex maestro ligador de Partagás) o confusión con ARLONDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombre de pila común</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registrar con apellido y firma; no sugerir vínculo</t>
+    <t xml:space="preserve">Asociación con Arnaldo Vichot (ex maestro ligador de Partagás) o confusión con DON VALLES / ARLONDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre de pila común (atenuado por el apellido); DON VALLES registrada en EE. UU. para puros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marca con nombre y apellido (ARNALDO VALLÉS) y firma; no sugerir vínculo</t>
   </si>
   <si>
     <t xml:space="preserve">Informe de registrabilidad</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">R22</t>
   </si>
   <si>
-    <t xml:space="preserve">Oposición o colisión de la marca ARNALDO en clase 34</t>
+    <t xml:space="preserve">Oposición o colisión de la marca ARNALDO VALLÉS en clase 34</t>
   </si>
   <si>
     <t xml:space="preserve">Búsqueda preliminar no oficial</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">DL 203/1999 de marcas; registro OCPI vía agente oficial</t>
   </si>
   <si>
-    <t xml:space="preserve">Necesario registrar ARNALDO (a nombre de la SL) en Cuba</t>
+    <t xml:space="preserve">Necesario registrar ARNALDO VALLÉS (a nombre de la SL) en Cuba</t>
   </si>
   <si>
     <t xml:space="preserve">PROBABLE (S42)</t>
@@ -2314,7 +2314,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
         <v>150</v>
       </c>
@@ -2354,7 +2354,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
         <v>156</v>
       </c>
